--- a/report_gen_wyscout/chat_errors.xlsx
+++ b/report_gen_wyscout/chat_errors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>question</t>
   </si>
@@ -296,6 +296,70 @@
     <t>Write a paragraph highlighting the physical strengths and weaknesses of the player Natalia Ramos in the position ofensive midfielder with a SWOT style. The parameters we are evaluating are; ['PSV-99', 'Distancia corriendo /90', 'Distancia corriendo \n a alta intensidad /90', 'Distancia a Sprint /90', 'Número de actividades \n a alta intensidad /90', 'Número de aceleraciones \n medias /90', 'Número de \n aceleraciones altas /90', 'Número de decelaraciones \n medias /90', 'Número de \n decelaraciones altas /90', 'Número de aceleraciones \n explosivas a Sprint /90']. The player's values are: [24, 1623, 339, 14, 30, 127, 2, 103, 9, 0]. The average values are: [25, 1169, 372, 63, 35, 99, 3, 84, 8, 0]</t>
   </si>
   <si>
+    <t>Write a paragraph highlighting the ofensive strengths and weaknesses of the player J. Ginzo in the position fullback with a SWOT style. The parameters we are evaluating are; ['Duelos ganados, %', 'Duelos aéreos ganados, %', 'Duelos atacantes ganados, %', 'Regates realizados, %', 'Precisión pases, %', 'Pases en profundidad/90', 'Pases/90', 'Precisión pases largos, %', 'Aceleraciones/90', 'Goles', 'Precisión centros, %', 'Centros al área pequeña/90', 'Precisión pases en el último tercio, %', 'Precisión pases en profundidad, %', 'Precisión pases progresivos, %', 'Tiros a la portería, %', 'Centros/90', 'Jugadas claves/90', 'Asistencias/90', 'xG/90']. The player's values are: Duelos ganados, %                          50.0
+Duelos aéreos ganados, %                  41.46
+Duelos atacantes ganados, %               42.59
+Regates realizados, %                     52.63
+Precisión pases, %                        77.43
+Pases en profundidad/90                    0.07
+Pases/90                                  37.45
+Precisión pases largos, %                 56.34
+Aceleraciones/90                           0.21
+Goles                                         1
+Precisión centros, %                      28.57
+Centros al área pequeña/90                 0.07
+Precisión pases en el último tercio, %    66.18
+Precisión pases en profundidad, %           0.0
+Precisión pases progresivos, %             70.8
+Tiros a la portería, %                     50.0
+Centros/90                                 2.45
+Jugadas claves/90                          0.49
+Asistencias/90                             0.07
+xG/90                                      0.02
+Name: 6, dtype: object. The average values are: Duelos ganados, %                         54.678077
+Duelos aéreos ganados, %                  48.826538
+Duelos atacantes ganados, %               47.107885
+Regates realizados, %                     60.933846
+Precisión pases, %                        72.926346
+Pases en profundidad/90                    0.376346
+Pases/90                                  32.428077
+Precisión pases largos, %                 45.055577
+Aceleraciones/90                           0.266346
+Goles                                      0.461538
+Precisión centros, %                      30.970962
+Centros al área pequeña/90                 0.296731
+Precisión pases en el último tercio, %    61.236346
+Precisión pases en profundidad, %         25.803462
+Precisión pases progresivos, %            69.187692
+Tiros a la portería, %                    25.128077
+Centros/90                                 2.321346
+Jugadas claves/90                          0.264808
+Asistencias/90                             0.047500
+xG/90                                      0.044231
+dtype: float64</t>
+  </si>
+  <si>
+    <t>Write a paragraph highlighting the defensive strengths and weaknesses of the player J. Ginzo in the position fullback with a SWOT style. The parameters we are evaluating are; ['Duelos ganados, %', 'Duelos aéreos ganados, %', 'Duelos defensivos/90', 'Duelos defensivos ganados, %', 'Duelos/90', 'Tiros interceptados/90', 'Interceptaciones/90', 'Acciones defensivas realizadas/90', 'Faltas/90']. The player's values are: Duelos ganados, %                     50.0
+Duelos aéreos ganados, %             41.46
+Duelos defensivos/90                  7.62
+Duelos defensivos ganados, %         60.55
+Duelos/90                            16.21
+Tiros interceptados/90                0.07
+Interceptaciones/90                   3.84
+Acciones defensivas realizadas/90     8.94
+Faltas/90                             1.12
+Name: 6, dtype: object. The average values are: Duelos ganados, %                    54.678077
+Duelos aéreos ganados, %             48.826538
+Duelos defensivos/90                  6.375962
+Duelos defensivos ganados, %         65.146731
+Duelos/90                            15.539231
+Tiros interceptados/90                0.187885
+Interceptaciones/90                   3.905769
+Acciones defensivas realizadas/90     8.452692
+Faltas/90                             0.950192
+dtype: float64</t>
+  </si>
+  <si>
     <t>The server had an error while processing your request. Sorry about that! {
   "error": {
     "message": "The server had an error while processing your request. Sorry about that!",
@@ -310,6 +374,9 @@
   </si>
   <si>
     <t>Invalid response object from API: '{\n  "error": {\n    "message": "Incorrect API key provided: sk-4OAKu***************************************r8cb. You can find your API key at https://platform.openai.com/account/api-keys.",\n    "type": "invalid_request_error",\n    "code": "invalid_api_key",\n    "param": null\n  },\n  "status": 401\n}' (HTTP response code was 401)</t>
+  </si>
+  <si>
+    <t>Invalid response object from API: '{\n  "error": {\n    "message": "Incorrect API key provided: sk-proj-********************************************************************************************************************************************************XsIA. You can find your API key at https://platform.openai.com/account/api-keys.",\n    "type": "invalid_request_error",\n    "code": "invalid_api_key",\n    "param": null\n  },\n  "status": 401\n}' (HTTP response code was 401)</t>
   </si>
 </sst>
 </file>
@@ -667,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -683,7 +750,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -691,7 +758,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -699,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -707,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -715,7 +782,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -723,7 +790,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -731,7 +798,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -739,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -747,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -755,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -763,7 +830,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -771,7 +838,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -779,7 +846,23 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
